--- a/static/spark-cv/data/cv_entries.xlsx
+++ b/static/spark-cv/data/cv_entries.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\spark\Documents\spark-webs\spark-web\public\spark-cv\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seonggpa\Documents\spark-web\spark-hydro.github.io\static\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD8A128-99A9-4D3E-95BE-1B880610A46C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88FBF25B-C6A9-482B-866D-CDD0DE5C4A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{658FACE9-883F-4F49-B936-65547CAA7E51}"/>
+    <workbookView xWindow="570" yWindow="570" windowWidth="32040" windowHeight="15375" xr2:uid="{658FACE9-883F-4F49-B936-65547CAA7E51}"/>
   </bookViews>
   <sheets>
     <sheet name="cv_entries" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="179">
   <si>
     <t>type</t>
   </si>
@@ -114,18 +114,6 @@
     <t>service</t>
   </si>
   <si>
-    <t>Faculty Advisory Committee: Research Advanced Computing Services</t>
-  </si>
-  <si>
-    <t>August, 2015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panel Member, Next Generation Assessment Review for Accessibility for Students with Disabilities </t>
-  </si>
-  <si>
-    <t>Sponsored by HumRRO and the Thomas B. Fordham Institute</t>
-  </si>
-  <si>
     <t>workshop-delivered</t>
   </si>
   <si>
@@ -168,9 +156,6 @@
     <t>affiliation</t>
   </si>
   <si>
-    <t>https://hpcf.uoregon.edu</t>
-  </si>
-  <si>
     <t>current</t>
   </si>
   <si>
@@ -183,9 +168,6 @@
     <t>Maximizing pilot phase measures to inform quality improvement: Using a sequential mixed methods design with interrupted time series to examine feasibility, uptake, and drivers of an evidence based practice in part c/early intervention systems</t>
   </si>
   <si>
-    <t>Core Member (two-year appointment): Social Systems Data Science Network</t>
-  </si>
-  <si>
     <t>2020</t>
   </si>
   <si>
@@ -195,9 +177,6 @@
     <t>Two-day workshop lead by Dr. Bradley Boehmke</t>
   </si>
   <si>
-    <t>COE Quantitative Curriculum Review Committee Member</t>
-  </si>
-  <si>
     <t>*Dissertation:* Dissertation: Enhancement of Coupled Surface/Subsurface Flow Models in Watersheds: Analysis, Model Development, Optimization, and User Accessibility</t>
   </si>
   <si>
@@ -453,18 +432,9 @@
     <t>Committee member</t>
   </si>
   <si>
-    <t>Fall 2023</t>
-  </si>
-  <si>
     <t>committee</t>
   </si>
   <si>
-    <t>Ali Akram Niazi from Parkistan, Ph.D program in Water Management &amp; Hydrological Science (WMHS), Texas A&amp;M University, Chair: Huilin Gao (WMHS)</t>
-  </si>
-  <si>
-    <t>College Station, Texas, United States</t>
-  </si>
-  <si>
     <t>July 24-26, 2024</t>
   </si>
   <si>
@@ -571,6 +541,36 @@
   </si>
   <si>
     <t>CE 3354: Engineering Hydrology</t>
+  </si>
+  <si>
+    <t>CECE Communications Committee</t>
+  </si>
+  <si>
+    <t>[Special Issue "Integrated Hydrologic Modeling and Data-Driven Decision Support"](https://https://www.mdpi.com/journal/water/special_issues/9U1DGD4N19?utm_source=linkedin&amp;utm_campaign=water&amp;utm_medium=social_journ), Water</t>
+  </si>
+  <si>
+    <t>Spring 2026</t>
+  </si>
+  <si>
+    <t>4.3/5</t>
+  </si>
+  <si>
+    <t>3.3/5</t>
+  </si>
+  <si>
+    <t>Summer 2026</t>
+  </si>
+  <si>
+    <t>Chair</t>
+  </si>
+  <si>
+    <t>CECE, Texas Tech University</t>
+  </si>
+  <si>
+    <t>David Serrano, Ph.D., Civil, Environmental, and Construction Engineering</t>
+  </si>
+  <si>
+    <t>Aunjishu Shrabonti, M.S., Civil, Environmental, and Construction Engineering</t>
   </si>
 </sst>
 </file>
@@ -662,7 +662,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -697,8 +697,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1023,19 +1021,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D849796-8D2F-2144-8637-FA01837A8DE5}">
   <dimension ref="A1:L70"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.09765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="74.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="49.3984375" customWidth="1"/>
+    <col min="2" max="2" width="10.08203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.4140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="74.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="49.4140625" customWidth="1"/>
     <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="35.3984375" customWidth="1"/>
-    <col min="9" max="9" width="27.59765625" customWidth="1"/>
+    <col min="8" max="8" width="35.4140625" customWidth="1"/>
+    <col min="9" max="9" width="27.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1052,10 +1050,10 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="G1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H1" t="s">
         <v>5</v>
@@ -1067,13 +1065,13 @@
         <v>6</v>
       </c>
       <c r="K1" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="L1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1084,30 +1082,30 @@
         <v>2018</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="E2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="F2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="J2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -1118,27 +1116,27 @@
         <v>2006</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E4" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F4" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="J4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -1149,57 +1147,57 @@
         <v>2004</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F6" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="J6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="E7" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="F7" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H8" s="9"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1207,21 +1205,21 @@
         <v>21</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E9" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F9" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H9" s="1"/>
       <c r="L9" s="5"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1232,77 +1230,77 @@
         <v>21</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E10" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="F10" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="H10" s="1"/>
       <c r="L10" s="5"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E11" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F11" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H11" s="1"/>
       <c r="L11" s="5"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E12" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F12" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H12" s="1"/>
       <c r="L12" s="5"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -1317,7 +1315,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -1332,7 +1330,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -1347,7 +1345,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -1362,762 +1360,781 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>49</v>
+        <v>131</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19">
-        <v>2018</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="I19" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+      <c r="F18" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D19" s="13"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+    </row>
+    <row r="20" spans="1:9" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="B20">
-        <v>2019</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>45</v>
+        <v>2026</v>
+      </c>
+      <c r="C20">
+        <v>2027</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="62" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" t="s">
-        <v>27</v>
+        <v>124</v>
+      </c>
+      <c r="B21">
+        <v>2022</v>
+      </c>
+      <c r="C21">
+        <v>2023</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>29</v>
+        <v>125</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>126</v>
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
-    </row>
-    <row r="22" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="D22" s="13"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-    </row>
-    <row r="23" spans="1:9" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="I21" s="19"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="E22" s="20"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="I22" s="19"/>
+    </row>
+    <row r="23" spans="1:9" ht="31" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>131</v>
-      </c>
-      <c r="B23">
-        <v>2022</v>
-      </c>
-      <c r="C23">
-        <v>2023</v>
+        <v>132</v>
+      </c>
+      <c r="B23" t="s">
+        <v>174</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>132</v>
+        <v>175</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="F23" s="4"/>
+        <v>177</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>176</v>
+      </c>
       <c r="G23" s="4"/>
       <c r="I23" s="19"/>
     </row>
-    <row r="24" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="31" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B24" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="F24" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="I24" s="19"/>
+    </row>
+    <row r="25" spans="1:9" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>132</v>
+      </c>
+      <c r="B25" t="s">
+        <v>145</v>
+      </c>
+      <c r="C25">
+        <v>2025</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E25" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="G24" s="4"/>
-    </row>
-    <row r="25" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>140</v>
-      </c>
-      <c r="B25" t="s">
-        <v>155</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E25" s="20" t="s">
+      <c r="F25" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="G25" s="4"/>
+    </row>
+    <row r="26" spans="1:9" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>132</v>
+      </c>
+      <c r="B26" t="s">
+        <v>145</v>
+      </c>
+      <c r="C26">
+        <v>2025</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="G26" s="4"/>
+    </row>
+    <row r="27" spans="1:9" s="22" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D27" s="23"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>164</v>
+      </c>
+      <c r="B28" t="s">
+        <v>171</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="G28" s="4">
+        <v>36</v>
+      </c>
+      <c r="H28" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>164</v>
+      </c>
+      <c r="B29" t="s">
+        <v>165</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="G29" s="4">
+        <v>57</v>
+      </c>
+      <c r="H29" t="s">
         <v>173</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="G25" s="4"/>
-    </row>
-    <row r="26" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>140</v>
-      </c>
-      <c r="B26" t="s">
-        <v>139</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E26" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="G26" s="4"/>
-    </row>
-    <row r="27" spans="1:9" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="D27" s="25"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>174</v>
-      </c>
-      <c r="B28" t="s">
-        <v>175</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="E28" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="G28" s="4">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E29" s="20"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
     </row>
-    <row r="31" spans="1:9" s="15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" s="15" customFormat="1" x14ac:dyDescent="0.35">
       <c r="D31" s="17"/>
       <c r="E31" s="18"/>
       <c r="F31" s="18"/>
       <c r="G31" s="18"/>
     </row>
-    <row r="32" spans="1:9" s="15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" s="15" customFormat="1" x14ac:dyDescent="0.35">
       <c r="D32" s="17"/>
       <c r="E32" s="18"/>
       <c r="F32" s="18"/>
       <c r="G32" s="18"/>
     </row>
-    <row r="33" spans="1:7" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>30</v>
-      </c>
-      <c r="B33"/>
+        <v>26</v>
+      </c>
       <c r="C33" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="G33" s="3">
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C34" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="G34" s="3">
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C35" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="G35" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C36" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="G36" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C37" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="G37" s="3">
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C38" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="G38" s="3">
         <v>39</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C39" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="G39" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C40" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="G40" s="3">
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C41" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="G41" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C42" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="G42" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C43" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E43" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="F43" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="G43">
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:7" s="15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" s="15" customFormat="1" x14ac:dyDescent="0.35">
       <c r="D44" s="16"/>
     </row>
-    <row r="45" spans="1:7" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>100</v>
-      </c>
-      <c r="C45" s="22" t="s">
-        <v>169</v>
-      </c>
-      <c r="D45" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="E45" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="F45" s="23" t="s">
-        <v>172</v>
-      </c>
-      <c r="G45" s="23">
+        <v>93</v>
+      </c>
+      <c r="C45" t="s">
+        <v>159</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="G45" s="3">
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C46" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="E46" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="G46">
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C47" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="E47" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="F47" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="G47">
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C48" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="E48" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="G48">
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C49" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="E49" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="F49" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="G49">
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C50" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E50" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="F50" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="G50">
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C51" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="E51" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F51" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="G51">
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C52" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="E52" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F52" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G52">
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B53" s="21"/>
       <c r="C53" s="21" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E53" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F53" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="G53">
         <v>17</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D54" s="3"/>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D55" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>37</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>37</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>37</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>37</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>41</v>
-      </c>
-      <c r="D56" s="1" t="s">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>37</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>41</v>
-      </c>
-      <c r="D57" s="1" t="s">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>37</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>41</v>
-      </c>
-      <c r="D58" s="1" t="s">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>37</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>41</v>
-      </c>
-      <c r="D59" s="1" t="s">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>37</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>41</v>
-      </c>
-      <c r="D60" s="1" t="s">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>37</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>41</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>41</v>
-      </c>
-      <c r="D62" s="1" t="s">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>41</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>41</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>42</v>
       </c>
       <c r="C65">
         <v>2017</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E65" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="H65" s="10">
         <v>5000</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C66">
         <v>2016</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E66" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="H66" s="11">
         <v>5000</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C67">
         <v>2014</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E67" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H67" s="10">
         <v>24000</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B70">
         <v>2018</v>
@@ -2126,13 +2143,13 @@
         <v>2019</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E70" t="s">
         <v>10</v>
       </c>
       <c r="H70" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
